--- a/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-coverage.xlsx
+++ b/jpcore-r4/copilot/high-priority-translation-issues/StructureDefinition-jp-coverage.xlsx
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>The Coverage resource contains the insurance card level information, which is customary to provide on claims and other communications between providers and insurers.  
-Coverageには、保険証レベルの情報が含まれている。これは、保険金請求やプロバイダと保険会社間のその他の通信で提供するのが通例である。</t>
+Coverageには、保険証レベルの情報が含まれている。これは、保険金請求や医療提供者と保険会社間のその他の通信で提供するのが通例である。</t>
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -549,14 +549,14 @@
 </t>
   </si>
   <si>
-    <t>Business Identifier for the coverage　このカバレッジに割り当てられた一意の識別子【詳細参照】</t>
-  </si>
-  <si>
-    <t>A unique identifier assigned to this coverage.  このカバレッジに割り当てられた一意の識別子。</t>
+    <t>Business Identifier for the coverage　この保険適用情報に割り当てられた一意の識別子【詳細参照】</t>
+  </si>
+  <si>
+    <t>A unique identifier assigned to this coverage.  この保険適用情報に割り当てられた一意の識別子。</t>
   </si>
   <si>
     <t>Allows coverages to be distinguished and referenced.  
-カバレッジを区別して参照できるようにする。</t>
+保険適用情報を区別して参照できるようにする。</t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
@@ -826,7 +826,7 @@
   </si>
   <si>
     <t>The main (and possibly only) identifier for the coverage - often referred to as a Member Id, Certificate number, Personal Health Number or Case ID. May be constructed as the concatenation of the Coverage.SubscriberID and the Coverage.dependent.  
-カバレッジのメイン（および場合によっては唯一の）識別子-多くの場合、メンバID、証明書番号、個人の健康番号、またはケースIDと呼ばれる。  
+保険適用情報のメイン（および場合によっては唯一の）識別子-多くの場合、会員番号、証明書番号、個人健康識別子、または症例IDと呼ばれる。  
 【JP Core仕様】被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
 ルール："{保険者番号:半角英数８桁}","{被保険者記号}","{被保険者番号}","{枝番:半角数字２桁}"  
 例："00012345","１２－３４","５６７８","00"</t>
@@ -857,7 +857,7 @@
   </si>
   <si>
     <t>The main (and possibly only) identifier for the coverage - often referred to as a Member Id, Certificate number, Personal Health Number or Case ID. May be constructed as the concatenation of the Coverage.SubscriberID and the Coverage.dependent.  
-カバレッジのメイン（および場合によっては唯一の）識別子-多くの場合、メンバID、証明書番号、個人の健康番号、またはケースIDと呼ばれる。  
+保険適用情報のメイン（および場合によっては唯一の）識別子-多くの場合、会員番号、証明書番号、個人健康識別子、または症例IDと呼ばれる。  
 【JP Core仕様】保険者番号と被保険者記号と番号と枝番を全角にした上でダブルコーテーションで囲い、カンマ区切りで連結する。  
 ルール："{保険者番号:半角英数８桁}","{被保険者記号}","{被保険者番号}","{枝番:半角数字２桁}"  
 例："00012345","１２－３４","５６７８","00"
@@ -887,7 +887,7 @@
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains the code entered-in-error that marks the coverage as not currently valid.  
-ステータスには、カバレッジが現在無効であることを示すエラー入力されたコードが含まれているため、この要素は修飾子としてラベル付けされる。</t>
+ステータスには、保険適用情報が現在無効であることを示すエラー入力されたコードが含まれているため、この要素は修飾子としてラベル付けされる。</t>
   </si>
   <si>
     <t>Need to track the status of the resource as 'draft' resources may undergo further edits while 'active' resources are immutable and may only have their status changed to 'cancelled'.  
@@ -925,7 +925,7 @@
   </si>
   <si>
     <t>The order of application of coverages is dependent on the types of coverage.  
-カバレッジの適用順序は、カバレッジのタイプによって異なる。</t>
+保険適用の適用順序は、保険適用のタイプによって異なる。</t>
   </si>
   <si>
     <t>保険の種類：公衆衛生、労働者補償。個人的な事故、自動車、民間の健康など）または個人または組織による直接支払い。 / The type of insurance: public health, worker compensation; private accident, auto, private health, etc.) or a direct payment by an individual or organization.</t>
@@ -1226,7 +1226,7 @@
   </si>
   <si>
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.  
-すべての用語の使用がこの一般的なパターンに適合するわけではない。いくつかのケースでは、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係、および前後の調整を管理するための独自の構造を提供することが望ましい。</t>
+すべての用語の使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、Codingを直接使用し、テキスト、コーディング、翻訳、要素間の関係、および事前・事後の用語結合を管理するための独自の構造を提供することが望ましい。</t>
   </si>
   <si>
     <t>The insurer issued label for a specific health card value.  
@@ -1291,7 +1291,7 @@
   </si>
   <si>
     <t>The order of applicability of this coverage relative to other coverages which are currently in force. Note, there may be gaps in the numbering and this does not imply primary, secondary etc. as the specific positioning of coverages depends upon the episode of care.  
-現在適用されている他の保障と比較して、この保障の適用可能性が高い順に記載されている。なお、ナンバリングにギャップがある場合があり、カバーの具体的な位置づけはケアのエピソードに依存するため、一次、二次などを意味するものではない。</t>
+現在適用されている他の保障と比較して、この保障の適用可能性が高い順に記載されている。なお、採番にギャップがある場合があり、適用範囲の具体的な位置づけは診療エピソードに依存するため、一次、二次などを意味するものではない。</t>
   </si>
   <si>
     <t>32 bit number; for values larger than this, use decimal  
@@ -1310,7 +1310,7 @@
   </si>
   <si>
     <t>The insurer-specific identifier for the insurer-defined network of providers to which the beneficiary may seek treatment which will be covered at the 'in-network' rate, otherwise 'out of network' terms and conditions apply.  
-保険者が定義したプロバイダの保険者定義ネットワークの保険者固有の識別子で、被保険者が「ネットワーク内」の料金でカバーされる治療を受けることができるが、そうでなければ「ネットワーク外」の条件が適用される。</t>
+保険者が定義した医療提供者の保険者定義ネットワークの保険者固有の識別子で、被保険者が「ネットワーク内」の料金でカバーされる治療を受けることができるが、そうでなければ「ネットワーク外」の条件が適用される。</t>
   </si>
   <si>
     <t>Used in referral for treatment and in claims processing.  
@@ -1472,8 +1472,7 @@
     <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size  
-自己負担率を表すコード　"copaypct"</t>
+    <t>自己負担率を表すコード　"copaypct"</t>
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
